--- a/aws_cost_dashboard_v5.xlsx
+++ b/aws_cost_dashboard_v5.xlsx
@@ -1,9 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+  <fileVersion appName="xl"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
@@ -17,11 +16,6 @@
     <sheet name="How_It_Works" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
